--- a/data/trans_dic/IP11C$nada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria</t>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,83</t>
+          <t>0,0; 43,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,39</t>
+          <t>0,0; 59,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,41</t>
+          <t>0,0; 27,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,12</t>
+          <t>0,0; 32,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,87</t>
+          <t>0,0; 39,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,95</t>
+          <t>0,0; 73,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,81</t>
+          <t>0,0; 34,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,46</t>
+          <t>0,0; 48,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 30,21</t>
+          <t>3,27; 29,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,48</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,55</t>
+          <t>0,0; 37,94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,34</t>
+          <t>0,0; 62,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,03; 76,14</t>
+          <t>31,52; 80,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,17 +1017,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,86</t>
+          <t>0,0; 51,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,76; 69,47</t>
+          <t>25,25; 65,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 39,14</t>
+          <t>5,01; 39,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,58; 66,98</t>
+          <t>34,06; 65,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,37</t>
+          <t>0,0; 86,47</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 64,81</t>
+          <t>7,57; 64,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,45; 75,15</t>
+          <t>15,89; 68,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,96</t>
+          <t>0,0; 49,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,9; 59,81</t>
+          <t>20,22; 59,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,2</t>
+          <t>0,0; 30,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1287,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1301,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,24 +1322,24 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,08</t>
+          <t>0,0; 66,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,98; 81,4</t>
+          <t>24,68; 81,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,37</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,22</t>
+          <t>0,0; 71,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,15</t>
+          <t>0,0; 80,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 44,82</t>
+          <t>8,23; 45,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,16; 74,18</t>
+          <t>11,27; 73,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,76; 85,92</t>
+          <t>14,34; 86,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,13; 53,21</t>
+          <t>19,07; 54,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,52; 60,79</t>
+          <t>7,69; 60,52</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,33</t>
+          <t>0,0; 60,57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,78; 69,93</t>
+          <t>9,82; 69,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,41; 83,6</t>
+          <t>40,14; 87,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,72</t>
+          <t>0,0; 25,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,45; 57,25</t>
+          <t>22,48; 55,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,67</t>
+          <t>0,0; 65,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 36,95</t>
+          <t>7,32; 36,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,75; 65,02</t>
+          <t>35,67; 62,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,88</t>
+          <t>0,0; 47,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,7</t>
+          <t>0,0; 62,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,06</t>
+          <t>0,0; 44,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,7</t>
+          <t>0,0; 38,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,65</t>
+          <t>0,0; 35,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,5</t>
+          <t>0,0; 25,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,2; 40,43</t>
+          <t>16,7; 40,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,63; 52,6</t>
+          <t>29,18; 51,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,7; 31,92</t>
+          <t>3,8; 35,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,76; 25,43</t>
+          <t>8,31; 26,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,51</t>
+          <t>17,87; 34,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,45; 26,39</t>
+          <t>8,11; 28,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,38; 28,35</t>
+          <t>14,11; 29,08</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25,12; 38,15</t>
+          <t>25,25; 38,74</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,19; 19,41</t>
+          <t>5,7; 18,58</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 16,92</t>
+          <t>1,9; 17,67</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente no necesitaron asistencia sanitaria (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3305</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3648</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3314</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2737</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3785</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2153</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3505</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3273</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>649; 5952</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2607</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3043</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6393</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12606</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3512</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3568; 9170</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1875</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3178</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3467; 8985</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1966</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>592; 4625</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8533; 16429</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2226</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3321</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>517; 4379</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1271; 5513</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3842</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2999; 8819</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3896</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1352</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1352</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2790</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2089</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2790</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2708</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4222</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2166</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2599</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>7319</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1945; 6419</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2836</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2461</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2571</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1082; 6032</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>673; 4408</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>656; 3935</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>4011; 11505</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>732; 5761</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3503</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7808</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>15749</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>672; 4790</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4799; 10515</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2927</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4601; 11408</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2569</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1356; 6850</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>11566; 20251</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3130</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3068</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2492</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3326</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4695</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2475</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>9737</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20980</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>17189</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>39538</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>5896; 14142</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>15090; 26797</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3583</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>652; 6040</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3867; 12335</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>13112; 25075</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3301; 11436</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3557</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>11547; 23800</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>31581; 48464</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3650; 11910</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>781; 7278</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$nada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Provincia-trans_dic.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,87</t>
+          <t>0,0; 44,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,17</t>
+          <t>0,0; 55,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,31</t>
+          <t>0,0; 26,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,04</t>
+          <t>0,0; 35,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,19</t>
+          <t>0,0; 41,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,35</t>
+          <t>0,0; 33,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,12</t>
+          <t>0,0; 48,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 29,97</t>
+          <t>3,22; 27,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,45</t>
+          <t>0,0; 26,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,94</t>
+          <t>0,0; 43,15</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,91</t>
+          <t>0,0; 62,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,52; 80,99</t>
+          <t>30,95; 81,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,08</t>
+          <t>0,0; 42,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,25; 65,44</t>
+          <t>24,76; 66,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 39,18</t>
+          <t>5,02; 38,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,06; 65,59</t>
+          <t>33,86; 66,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,47</t>
+          <t>0,0; 85,69</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 64,09</t>
+          <t>8,14; 65,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,89; 68,94</t>
+          <t>16,91; 75,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,04</t>
+          <t>0,0; 42,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,22; 59,47</t>
+          <t>17,94; 60,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,48</t>
+          <t>0,0; 32,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,66</t>
+          <t>0,0; 66,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1422,32 +1422,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,68; 81,47</t>
+          <t>18,87; 81,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 82,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,1</t>
+          <t>0,0; 73,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,01</t>
+          <t>0,0; 80,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,23; 45,87</t>
+          <t>8,78; 46,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,27; 73,78</t>
+          <t>11,34; 74,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,34; 86,05</t>
+          <t>26,01; 86,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,07; 54,71</t>
+          <t>18,91; 53,29</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,69; 60,52</t>
+          <t>7,66; 61,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,57</t>
+          <t>0,0; 54,81</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 69,97</t>
+          <t>9,81; 70,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,14; 87,96</t>
+          <t>41,32; 83,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,06</t>
+          <t>0,0; 30,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,48; 55,73</t>
+          <t>21,95; 56,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,61</t>
+          <t>0,0; 64,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,32; 36,97</t>
+          <t>7,25; 36,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,67; 62,45</t>
+          <t>34,94; 62,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,58</t>
+          <t>0,0; 38,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,94</t>
+          <t>0,0; 69,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,46</t>
+          <t>0,0; 43,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,96</t>
+          <t>0,0; 38,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,01</t>
+          <t>0,0; 31,96</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,57</t>
+          <t>0,0; 28,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,7; 40,06</t>
+          <t>16,38; 41,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,18; 51,82</t>
+          <t>29,94; 53,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>0,0; 17,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,8; 35,21</t>
+          <t>3,94; 33,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,31; 26,51</t>
+          <t>8,76; 26,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,87; 34,17</t>
+          <t>18,1; 34,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,11; 28,08</t>
+          <t>7,52; 26,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 12,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,11; 29,08</t>
+          <t>14,35; 28,66</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25,25; 38,74</t>
+          <t>25,15; 38,38</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,7; 18,58</t>
+          <t>5,82; 18,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,67</t>
+          <t>2,01; 15,96</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3305</t>
+          <t>0; 3353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3648</t>
+          <t>0; 3425</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3314</t>
+          <t>0; 3232</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2737</t>
+          <t>0; 2991</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3785</t>
+          <t>0; 3977</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3456</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3273</t>
+          <t>0; 3288</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>649; 5952</t>
+          <t>640; 5384</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2607</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3043</t>
+          <t>0; 3461</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3512</t>
+          <t>0; 3465</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3568; 9170</t>
+          <t>3504; 9198</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3178</t>
+          <t>0; 2630</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3467; 8985</t>
+          <t>3400; 9136</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592; 4625</t>
+          <t>593; 4583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8533; 16429</t>
+          <t>8481; 16683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3321</t>
+          <t>0; 3291</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>517; 4379</t>
+          <t>556; 4502</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1271; 5513</t>
+          <t>1353; 6009</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 3308</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2999; 8819</t>
+          <t>2660; 8986</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3896</t>
+          <t>0; 4120</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2708</t>
+          <t>0; 2719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1945; 6419</t>
+          <t>1486; 6409</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2836</t>
+          <t>0; 2913</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2461</t>
+          <t>0; 2553</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2571</t>
+          <t>0; 2575</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1082; 6032</t>
+          <t>1155; 6171</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>673; 4408</t>
+          <t>678; 4446</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,22 +3289,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>656; 3935</t>
+          <t>1189; 3941</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4011; 11505</t>
+          <t>3976; 11208</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>732; 5761</t>
+          <t>729; 5834</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 3170</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>672; 4790</t>
+          <t>672; 4795</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4799; 10515</t>
+          <t>4939; 9999</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3477,17 +3477,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2927</t>
+          <t>0; 3580</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4601; 11408</t>
+          <t>4493; 11610</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2569</t>
+          <t>0; 2542</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1356; 6850</t>
+          <t>1343; 6852</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11566; 20251</t>
+          <t>11331; 20228</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>0; 2520</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3068</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2492</t>
+          <t>0; 2460</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3326</t>
+          <t>0; 3280</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 4286</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2475</t>
+          <t>0; 2766</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5896; 14142</t>
+          <t>5782; 14713</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15090; 26797</t>
+          <t>15485; 27624</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 3583</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>652; 6040</t>
+          <t>676; 5804</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3867; 12335</t>
+          <t>4075; 12342</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13112; 25075</t>
+          <t>13283; 24956</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3301; 11436</t>
+          <t>3063; 10637</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 3557</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11547; 23800</t>
+          <t>11747; 23448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31581; 48464</t>
+          <t>31462; 48005</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3650; 11910</t>
+          <t>3729; 11888</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>781; 7278</t>
+          <t>829; 6574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$nada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$nada-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,37 +649,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,74%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 47,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,64</t>
+          <t>0,0; 32,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,01</t>
+          <t>0,0; 36,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>13,18%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>12,99%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,18</t>
+          <t>0,0; 35,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,87</t>
+          <t>0,0; 38,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 74,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 27,11</t>
+          <t>3,3; 30,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,14</t>
+          <t>0,0; 21,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,15</t>
+          <t>0,0; 46,95</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45,26%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38,76%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>23,78%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>56,46%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46,79%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,07</t>
+          <t>0,0; 43,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,95; 81,24</t>
+          <t>24,76; 69,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,28</t>
+          <t>0,0; 68,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,76; 66,54</t>
+          <t>31,03; 76,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 38,82</t>
+          <t>5,0; 39,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33,86; 66,6</t>
+          <t>34,58; 66,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,69</t>
+          <t>0,0; 89,12</t>
         </is>
       </c>
     </row>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42,05%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,44%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>32,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 65,9</t>
+          <t>16,45; 75,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 75,14</t>
+          <t>7,21; 64,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,94; 60,6</t>
+          <t>19,9; 59,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,24</t>
+          <t>0,0; 26,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>48,46%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>33,01%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,34 +1277,34 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,93</t>
+          <t>0,0; 67,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38,57%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23,54%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36,25%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>53,59%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>20,83%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 80,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,87; 81,35</t>
+          <t>8,88; 44,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,18</t>
+          <t>11,16; 74,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 46,92</t>
+          <t>24,98; 81,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,34; 74,42</t>
+          <t>0,0; 80,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 73,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,01; 86,17</t>
+          <t>13,76; 85,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,91; 53,29</t>
+          <t>18,13; 53,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 61,29</t>
+          <t>7,52; 60,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,81</t>
+          <t>0,0; 61,06</t>
         </is>
       </c>
     </row>
@@ -1489,37 +1489,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>39,44%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>65,31%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,81; 70,04</t>
+          <t>0,0; 24,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41,32; 83,64</t>
+          <t>22,45; 57,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 63,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1577,17 +1577,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,65</t>
+          <t>9,78; 69,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,95; 56,71</t>
+          <t>40,41; 83,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 36,98</t>
+          <t>7,29; 36,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34,94; 62,38</t>
+          <t>35,75; 65,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,3</t>
+          <t>0,0; 38,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1629,32 +1629,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>16,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>10,61%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,74</t>
+          <t>0,0; 38,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,43</t>
+          <t>0,0; 69,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,96</t>
+          <t>0,0; 31,65</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,57</t>
+          <t>0,0; 31,5</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>25,29%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>27,58%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>40,57%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,38; 41,67</t>
+          <t>8,76; 25,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,94; 53,42</t>
+          <t>17,87; 34,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,91</t>
+          <t>7,45; 26,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 33,84</t>
+          <t>0,0; 13,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,76; 26,53</t>
+          <t>17,2; 40,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,1; 34,01</t>
+          <t>29,63; 52,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 26,12</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,79</t>
+          <t>4,12; 33,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,35; 28,66</t>
+          <t>14,38; 28,35</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25,15; 38,38</t>
+          <t>25,12; 38,15</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 18,55</t>
+          <t>6,19; 19,41</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 15,96</t>
+          <t>2,28; 17,29</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3152</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3232</t>
+          <t>0; 3933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2991</t>
+          <t>0; 3087</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2291,32 +2291,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2354,57 +2354,57 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1273</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2580</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>756</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3977</t>
+          <t>0; 3654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2616</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2153</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3456</t>
+          <t>0; 3754</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3288</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2361</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>640; 5384</t>
+          <t>654; 6000</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3177</t>
+          <t>0; 2611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>0; 3715</t>
         </is>
       </c>
     </row>
@@ -2489,37 +2489,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6393</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>877</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12606</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>1467</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>12606</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1505</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3465</t>
+          <t>0; 2729</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3504; 9198</t>
+          <t>3400; 9537</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>0; 1666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2630</t>
+          <t>0; 3815</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3400; 9136</t>
+          <t>3514; 8620</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>0; 1760</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>593; 4583</t>
+          <t>591; 4621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8481; 16683</t>
+          <t>8662; 16777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3291</t>
+          <t>0; 3053</t>
         </is>
       </c>
     </row>
@@ -2697,29 +2697,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,29 +2765,29 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2204</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>556; 4502</t>
+          <t>1316; 6010</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3522</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1353; 6009</t>
+          <t>493; 4428</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3308</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2660; 8986</t>
+          <t>2951; 8869</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4120</t>
+          <t>0; 3348</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2905,32 +2905,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1352</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>690</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>0; 2790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0; 2089</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 2726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2166</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4222</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2166</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>735</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2575</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1486; 6409</t>
+          <t>1167; 5895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2913</t>
+          <t>667; 4432</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2553</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2575</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1155; 6171</t>
+          <t>1968; 6413</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>678; 4446</t>
+          <t>0; 2849</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2503</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1189; 3941</t>
+          <t>629; 3929</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3976; 11208</t>
+          <t>3813; 11191</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>729; 5834</t>
+          <t>716; 5787</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3170</t>
+          <t>0; 3270</t>
         </is>
       </c>
     </row>
@@ -3321,37 +3321,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3389,37 +3389,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>7808</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7940</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>672; 4795</t>
+          <t>0; 2888</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4939; 9999</t>
+          <t>4595; 11720</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2493</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3477,17 +3477,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3580</t>
+          <t>670; 4787</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4493; 11610</t>
+          <t>4832; 9994</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2542</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1343; 6852</t>
+          <t>1351; 6847</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11331; 20228</t>
+          <t>11592; 21084</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2520</t>
+          <t>0; 2558</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3534,27 +3534,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>595</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>0; 3304</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2460</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 3280</t>
+          <t>0; 3398</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2470</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 4286</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2766</t>
+          <t>0; 3049</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>7452</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>18558</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>9737</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>20980</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>738</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2291</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>7452</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>18558</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2996</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5782; 14713</t>
+          <t>4075; 11831</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15485; 27624</t>
+          <t>13114; 25322</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>3033; 10746</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>676; 5804</t>
+          <t>0; 2912</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4075; 12342</t>
+          <t>6071; 14275</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13283; 24956</t>
+          <t>15323; 27200</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3063; 10637</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 3074</t>
+          <t>707; 5701</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11747; 23448</t>
+          <t>11767; 23199</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31462; 48005</t>
+          <t>31420; 47721</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3729; 11888</t>
+          <t>3964; 12439</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>829; 6574</t>
+          <t>900; 6818</t>
         </is>
       </c>
     </row>
